--- a/bombeio.xlsx
+++ b/bombeio.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Permanente\Comissao de Preco\Ygor\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9E1F89-CBFA-4EB0-A9C3-1380197F9EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0736D1-20F9-44C0-A0C8-A1DC24FB99FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bombeio" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -87,23 +100,27 @@
       <sz val="11"/>
       <color rgb="FF1A3E6F"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF5A7399"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -154,10 +171,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -471,22 +488,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -516,9 +533,9 @@
         <v>9</v>
       </c>
       <c r="D4" s="3">
-        <v>5.7561999999999998</v>
-      </c>
-      <c r="E4" s="7">
+        <v>5.8220999999999998</v>
+      </c>
+      <c r="E4" s="4">
         <v>46231</v>
       </c>
     </row>
@@ -533,9 +550,9 @@
         <v>10</v>
       </c>
       <c r="D5" s="3">
-        <v>5.7163000000000004</v>
-      </c>
-      <c r="E5" s="7">
+        <v>5.7821999999999996</v>
+      </c>
+      <c r="E5" s="4">
         <v>46231</v>
       </c>
     </row>
@@ -552,7 +569,7 @@
       <c r="D6" s="3">
         <v>4.9214000000000002</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="4">
         <v>46231</v>
       </c>
     </row>
@@ -569,7 +586,7 @@
       <c r="D7" s="3">
         <v>4.8925999999999998</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="4">
         <v>46231</v>
       </c>
     </row>
@@ -586,7 +603,7 @@
       <c r="D8" s="3">
         <v>4.8532000000000002</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="4">
         <v>46231</v>
       </c>
     </row>
@@ -603,7 +620,7 @@
       <c r="D9" s="3">
         <v>4.8287000000000004</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="4">
         <v>46231</v>
       </c>
     </row>
